--- a/artifacts/output/test4_output.xlsx
+++ b/artifacts/output/test4_output.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Schedule Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,11 +459,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>46083.33333333334</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46083.45833333334</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -485,11 +486,15 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>46083.33333333334</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46083.4375</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -508,11 +513,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>46083.33333333334</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46083.5</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -531,11 +540,15 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>46083.33333333334</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46083.39583333334</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -554,11 +567,15 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>46083.33333333334</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46083.41666666666</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -577,11 +594,37 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>46083.41666666666</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46083.45833333334</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Total Duration (hours)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/output/test4_output.xlsx
+++ b/artifacts/output/test4_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,22 +608,10 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
           <t>Total Duration (hours)</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B9" t="n">
         <v>14</v>
       </c>
     </row>
